--- a/benchmark_result/Книга1.xlsx
+++ b/benchmark_result/Книга1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GraphAlgo_RISC_V\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GraphAlgo_RISC_V\benchmark_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E6F8C3-0343-4407-8C44-E0C988F17638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABACAA1-7B8F-4187-BA84-CAE12F3B2EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C6F22A6A-250E-4553-97A4-2A823809E475}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="35">
   <si>
     <t>k_truss with k = 3 on main graphs</t>
   </si>
@@ -118,6 +118,33 @@
   </si>
   <si>
     <t>scalar/vec</t>
+  </si>
+  <si>
+    <t>k_truss with k = 3</t>
+  </si>
+  <si>
+    <t>k_truss with k = 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">triangle test </t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>vec</t>
+  </si>
+  <si>
+    <t>scal</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>Среднее ускорение</t>
+  </si>
+  <si>
+    <t>Среднее без webbase</t>
   </si>
 </sst>
 </file>
@@ -127,13 +154,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -145,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -153,15 +188,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1232,32 +1315,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA44E6C-A1D4-4D07-A2E2-64CFD1FF39E5}">
-  <dimension ref="D6:O45"/>
+  <dimension ref="D6:T45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="1"/>
     <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="4:15" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="4:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
+      <c r="E7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>25</v>
@@ -1268,15 +1358,21 @@
       <c r="O7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="R7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>489</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
         <v>488</v>
       </c>
       <c r="G8">
@@ -1298,15 +1394,23 @@
         <f>AND(J8="ВЕКТОР", M8=FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="R8" s="8">
+        <f>AVERAGE(I8:I16,I20:I28,I32:I45)</f>
+        <v>1.2631968142729815</v>
+      </c>
+      <c r="T8" s="8">
+        <f>AVERAGE(I8:I11,I13:I16,I20:I23,I25:I28,I32:I40,I42:I45)</f>
+        <v>1.0318817003161691</v>
+      </c>
+    </row>
+    <row r="9" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>716</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="5">
         <v>742</v>
       </c>
       <c r="G9">
@@ -1329,14 +1433,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>810</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="5">
         <v>833</v>
       </c>
       <c r="G10">
@@ -1359,14 +1463,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>833</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="5">
         <v>889</v>
       </c>
       <c r="G11">
@@ -1389,14 +1493,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>874</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="5">
         <v>3344</v>
       </c>
       <c r="G12">
@@ -1419,14 +1523,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>1301</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="5">
         <v>1418</v>
       </c>
       <c r="G13">
@@ -1449,14 +1553,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>15</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>1420</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="5">
         <v>1449</v>
       </c>
       <c r="G14">
@@ -1479,14 +1583,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>2931</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="5">
         <v>3578</v>
       </c>
       <c r="G15">
@@ -1509,14 +1613,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>6074</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="5">
         <v>7133</v>
       </c>
       <c r="G16">
@@ -1539,33 +1643,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>3</v>
       </c>
-      <c r="E19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s">
-        <v>8</v>
+      <c r="E19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>9</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>527</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="5">
         <v>532</v>
       </c>
       <c r="G20">
@@ -1592,10 +1703,10 @@
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>620</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="5">
         <v>629</v>
       </c>
       <c r="G21">
@@ -1622,10 +1733,10 @@
       <c r="D22" t="s">
         <v>11</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
         <v>723</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="5">
         <v>730</v>
       </c>
       <c r="G22">
@@ -1652,10 +1763,10 @@
       <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>740</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="5">
         <v>786</v>
       </c>
       <c r="G23">
@@ -1682,10 +1793,10 @@
       <c r="D24" t="s">
         <v>13</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>1876</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="5">
         <v>7692</v>
       </c>
       <c r="G24">
@@ -1712,10 +1823,10 @@
       <c r="D25" t="s">
         <v>14</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>1418</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="5">
         <v>1556</v>
       </c>
       <c r="G25">
@@ -1742,10 +1853,10 @@
       <c r="D26" t="s">
         <v>15</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="4">
         <v>1419</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="5">
         <v>1451</v>
       </c>
       <c r="G26">
@@ -1772,10 +1883,10 @@
       <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="4">
         <v>1815</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="5">
         <v>2162</v>
       </c>
       <c r="G27">
@@ -1802,10 +1913,10 @@
       <c r="D28" t="s">
         <v>17</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="4">
         <v>2795</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="5">
         <v>3178</v>
       </c>
       <c r="G28">
@@ -1828,33 +1939,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="4:15" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="4:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>3</v>
       </c>
-      <c r="E31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" t="s">
-        <v>8</v>
+      <c r="E31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>18</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="4">
         <v>5</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="5">
         <v>5</v>
       </c>
       <c r="G32">
@@ -1881,10 +1999,10 @@
       <c r="D33" t="s">
         <v>19</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="4">
         <v>12</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="5">
         <v>11</v>
       </c>
       <c r="G33">
@@ -1911,10 +2029,10 @@
       <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="4">
         <v>30</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="5">
         <v>20</v>
       </c>
       <c r="G34">
@@ -1941,10 +2059,10 @@
       <c r="D35" t="s">
         <v>21</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="4">
         <v>39</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="5">
         <v>38</v>
       </c>
       <c r="G35">
@@ -1971,10 +2089,10 @@
       <c r="D36" t="s">
         <v>22</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="4">
         <v>41</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="5">
         <v>41</v>
       </c>
       <c r="G36">
@@ -2001,10 +2119,10 @@
       <c r="D37" t="s">
         <v>9</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="4">
         <v>66</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="5">
         <v>67</v>
       </c>
       <c r="G37">
@@ -2031,10 +2149,10 @@
       <c r="D38" t="s">
         <v>10</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>49</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="5">
         <v>51</v>
       </c>
       <c r="G38">
@@ -2061,10 +2179,10 @@
       <c r="D39" t="s">
         <v>11</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="4">
         <v>52</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="5">
         <v>54</v>
       </c>
       <c r="G39">
@@ -2091,10 +2209,10 @@
       <c r="D40" t="s">
         <v>12</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="4">
         <v>558</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="5">
         <v>604</v>
       </c>
       <c r="G40">
@@ -2121,10 +2239,10 @@
       <c r="D41" t="s">
         <v>13</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>14</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="5">
         <v>36</v>
       </c>
       <c r="G41">
@@ -2151,10 +2269,10 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>366</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="5">
         <v>377</v>
       </c>
       <c r="G42">
@@ -2181,10 +2299,10 @@
       <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>186</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="5">
         <v>125</v>
       </c>
       <c r="G43">
@@ -2211,10 +2329,10 @@
       <c r="D44" t="s">
         <v>16</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>27</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="5">
         <v>32</v>
       </c>
       <c r="G44">
@@ -2241,10 +2359,10 @@
       <c r="D45" t="s">
         <v>17</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>81</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="5">
         <v>91</v>
       </c>
       <c r="G45">
@@ -2268,6 +2386,11 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E30:F30"/>
+  </mergeCells>
   <conditionalFormatting sqref="I8:I16 I20:I28 I32:I45">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>1</formula>

--- a/benchmark_result/Книга1.xlsx
+++ b/benchmark_result/Книга1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GraphAlgo_RISC_V\benchmark_result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denik\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABACAA1-7B8F-4187-BA84-CAE12F3B2EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4587B5-DBD2-4A98-8823-258BB50A3083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C6F22A6A-250E-4553-97A4-2A823809E475}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="37">
   <si>
     <t>k_truss with k = 3 on main graphs</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Среднее без webbase</t>
+  </si>
+  <si>
+    <t>Среднее k=3 без webbase</t>
+  </si>
+  <si>
+    <t>Среднее k=4 без webbase</t>
   </si>
 </sst>
 </file>
@@ -233,9 +239,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -245,6 +248,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1328,11 +1334,11 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1340,13 +1346,13 @@
       <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1369,10 +1375,10 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>489</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>488</v>
       </c>
       <c r="G8">
@@ -1394,11 +1400,11 @@
         <f>AND(J8="ВЕКТОР", M8=FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="7">
         <f>AVERAGE(I8:I16,I20:I28,I32:I45)</f>
         <v>1.2631968142729815</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="7">
         <f>AVERAGE(I8:I11,I13:I16,I20:I23,I25:I28,I32:I40,I42:I45)</f>
         <v>1.0318817003161691</v>
       </c>
@@ -1407,10 +1413,10 @@
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>716</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>742</v>
       </c>
       <c r="G9">
@@ -1437,10 +1443,10 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>810</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>833</v>
       </c>
       <c r="G10">
@@ -1467,10 +1473,10 @@
       <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>833</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>889</v>
       </c>
       <c r="G11">
@@ -1497,10 +1503,10 @@
       <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>874</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>3344</v>
       </c>
       <c r="G12">
@@ -1521,16 +1527,22 @@
       <c r="O12" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>35</v>
+      </c>
+      <c r="T12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>1301</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>1418</v>
       </c>
       <c r="G13">
@@ -1551,16 +1563,24 @@
       <c r="O13" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
+      </c>
+      <c r="R13" s="7">
+        <f>AVERAGE(I8:I11,I13:I16)</f>
+        <v>1.0794170787718331</v>
+      </c>
+      <c r="T13" s="7">
+        <f>AVERAGE(I20:I23,I25:I28)</f>
+        <v>1.0679917605378157</v>
       </c>
     </row>
     <row r="14" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>1420</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>1449</v>
       </c>
       <c r="G14">
@@ -1587,10 +1607,10 @@
       <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>2931</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>3578</v>
       </c>
       <c r="G15">
@@ -1617,10 +1637,10 @@
       <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>6074</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>7133</v>
       </c>
       <c r="G16">
@@ -1647,11 +1667,11 @@
       <c r="D18" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1659,13 +1679,13 @@
       <c r="D19" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1673,10 +1693,10 @@
       <c r="D20" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>527</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>532</v>
       </c>
       <c r="G20">
@@ -1703,10 +1723,10 @@
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>620</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>629</v>
       </c>
       <c r="G21">
@@ -1733,10 +1753,10 @@
       <c r="D22" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>723</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>730</v>
       </c>
       <c r="G22">
@@ -1763,10 +1783,10 @@
       <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>740</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>786</v>
       </c>
       <c r="G23">
@@ -1793,10 +1813,10 @@
       <c r="D24" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>1876</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>7692</v>
       </c>
       <c r="G24">
@@ -1823,10 +1843,10 @@
       <c r="D25" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>1418</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>1556</v>
       </c>
       <c r="G25">
@@ -1853,10 +1873,10 @@
       <c r="D26" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="3">
         <v>1419</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>1451</v>
       </c>
       <c r="G26">
@@ -1883,10 +1903,10 @@
       <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="3">
         <v>1815</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>2162</v>
       </c>
       <c r="G27">
@@ -1913,10 +1933,10 @@
       <c r="D28" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3">
         <v>2795</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>3178</v>
       </c>
       <c r="G28">
@@ -1943,11 +1963,11 @@
       <c r="D30" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="3" t="s">
+      <c r="F30" s="8"/>
+      <c r="G30" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1955,13 +1975,13 @@
       <c r="D31" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1969,10 +1989,10 @@
       <c r="D32" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>5</v>
       </c>
       <c r="G32">
@@ -1999,10 +2019,10 @@
       <c r="D33" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <v>12</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>11</v>
       </c>
       <c r="G33">
@@ -2029,10 +2049,10 @@
       <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>30</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="4">
         <v>20</v>
       </c>
       <c r="G34">
@@ -2059,10 +2079,10 @@
       <c r="D35" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="3">
         <v>39</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <v>38</v>
       </c>
       <c r="G35">
@@ -2089,10 +2109,10 @@
       <c r="D36" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>41</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>41</v>
       </c>
       <c r="G36">
@@ -2119,10 +2139,10 @@
       <c r="D37" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="3">
         <v>66</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="4">
         <v>67</v>
       </c>
       <c r="G37">
@@ -2149,10 +2169,10 @@
       <c r="D38" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="3">
         <v>49</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="4">
         <v>51</v>
       </c>
       <c r="G38">
@@ -2179,10 +2199,10 @@
       <c r="D39" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="3">
         <v>52</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="4">
         <v>54</v>
       </c>
       <c r="G39">
@@ -2209,10 +2229,10 @@
       <c r="D40" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="3">
         <v>558</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="4">
         <v>604</v>
       </c>
       <c r="G40">
@@ -2239,10 +2259,10 @@
       <c r="D41" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="3">
         <v>14</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="4">
         <v>36</v>
       </c>
       <c r="G41">
@@ -2269,10 +2289,10 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="3">
         <v>366</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="4">
         <v>377</v>
       </c>
       <c r="G42">
@@ -2299,10 +2319,10 @@
       <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="3">
         <v>186</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="4">
         <v>125</v>
       </c>
       <c r="G43">
@@ -2329,10 +2349,10 @@
       <c r="D44" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="3">
         <v>27</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="4">
         <v>32</v>
       </c>
       <c r="G44">
@@ -2359,10 +2379,10 @@
       <c r="D45" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="3">
         <v>81</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="4">
         <v>91</v>
       </c>
       <c r="G45">
